--- a/Codelist Excel Files and Conversion Templates to XML/designMethod.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/designMethod.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes naming the analytical approach a rigid inclusion design was calculated by. Used for the value of the designMethod property of diggs:RISystemBasis. RI_Design_Parameter_Analysis.md Group A row 3 names four approaches in current practice; the list is open, since design methods are not a closed set.</t>
+          <t>Codes naming the analytical approach a rigid inclusion design was calculated by. Used for the value of the designMethod property of diggs:RIProgramBasis. RI_Design_Parameter_Analysis.md Group A row 3 names four approaches in current practice; the list is open, since design methods are not a closed set.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:designMethod</t>
+          <t>//diggs:RIProgramBasis/diggs:designMethod</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:designMethod</t>
+          <t>//diggs:RIProgramBasis/diggs:designMethod</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:designMethod</t>
+          <t>//diggs:RIProgramBasis/diggs:designMethod</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//diggs:RISystemBasis/diggs:designMethod</t>
+          <t>//diggs:RIProgramBasis/diggs:designMethod</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/designMethod.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/designMethod.xlsx
@@ -1202,24 +1202,93 @@
         <f>IF(ISNA(VLOOKUP(B6,AssociatedElements!B$2:B2944,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="17" t="n"/>
-      <c r="G6" s="9" t="n"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fhwa_beam</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>FHWA beam method</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>The FHWA GEC-13 beam formulation (Eq 3-26), in which the load transfer platform is analysed as a beam or slab spanning between inclusion heads and the geosynthetic membrane contribution is taken through the membrane factor of GEC-13 Table 6-2. One of two FHWA variants a designer selects between; the other is fhwa_strain_compatibility.</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>FHWA GEC-13 (FHWA-NHI-16-028)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2">
         <f>IF(ISNA(VLOOKUP(B7,AssociatedElements!B$2:B2945,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G7" s="9" t="n"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fhwa_strain_compatibility</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>FHWA strain-compatibility method</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>The FHWA GEC-13 generalized parabolic formulation (Eq 3-25), which distributes load between the inclusion heads and the intervening soil by enforcing strain compatibility across the platform rather than assuming a fixed arching ratio. One of two FHWA variants a designer selects between; the other is fhwa_beam.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>FHWA GEC-13 (FHWA-NHI-16-028)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2">
         <f>IF(ISNA(VLOOKUP(B8,AssociatedElements!B$2:B2946,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="G8" s="9" t="n"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nordic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Nordic method</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>The Nordic (Scandinavian) design practice for column-supported embankments, carried as a distinct published method in practitioner surveys of rigid inclusion design.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2">
@@ -1671,21 +1740,48 @@
         <f>IF(ISNA(VLOOKUP(B6,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>fhwa_beam</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:designMethod</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
         <f>IF(ISNA(VLOOKUP(B7,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B7" s="2" t="n"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>fhwa_strain_compatibility</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:designMethod</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
         <f>IF(ISNA(VLOOKUP(B8,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B8" s="2" t="n"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>nordic</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>//diggs:RIProgramBasis/diggs:designMethod</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
